--- a/Script_8_multiple_factor_age:sex_and_age:region_interaction/GSEA/gsea summary.xlsx
+++ b/Script_8_multiple_factor_age:sex_and_age:region_interaction/GSEA/gsea summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/outobi/Downloads/final analysis/multiple factor interaction/interaction/aged * sex interction for reviewer/GSEA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/outobi/Downloads/final analysis/final code/rat-lung-proteomics/Script_8_multiple_factor_age:sex_and_age:region_interaction/GSEA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A40140-5FB4-EC4E-AC99-D2115E7FEE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4908F620-0C0D-6345-97C7-96CC76945F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4860" yWindow="4160" windowWidth="26440" windowHeight="15440" xr2:uid="{7A9B66F1-F78A-664C-8FC6-95C9136B040A}"/>
+    <workbookView xWindow="7800" yWindow="4100" windowWidth="26440" windowHeight="15440" xr2:uid="{7A9B66F1-F78A-664C-8FC6-95C9136B040A}"/>
   </bookViews>
   <sheets>
     <sheet name="ITEM SUMMARY" sheetId="8" r:id="rId1"/>
@@ -18,9 +18,8 @@
     <sheet name="female vs male reactome" sheetId="2" r:id="rId3"/>
     <sheet name="bottom vs peri GO" sheetId="3" r:id="rId4"/>
     <sheet name="central vs peri GO" sheetId="4" r:id="rId5"/>
-    <sheet name="central vs peri reactome" sheetId="5" r:id="rId6"/>
-    <sheet name="central vs top GO" sheetId="6" r:id="rId7"/>
-    <sheet name="central vs top reactome" sheetId="7" r:id="rId8"/>
+    <sheet name="central vs top GO" sheetId="6" r:id="rId6"/>
+    <sheet name="central vs top reactome" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
   <si>
     <t>GO</t>
   </si>
@@ -156,24 +155,6 @@
     <t>Nonsense Mediated Decay (NMD) enhanced by the Exon Junction Complex (EJC)</t>
   </si>
   <si>
-    <t>R-RNO-72706</t>
-  </si>
-  <si>
-    <t>GTP hydrolysis and joining of the 60S ribosomal subunit</t>
-  </si>
-  <si>
-    <t>R-RNO-1799339</t>
-  </si>
-  <si>
-    <t>SRP-dependent cotranslational protein targeting to membrane</t>
-  </si>
-  <si>
-    <t>R-RNO-72766</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
     <t>R-RNO-156827</t>
   </si>
   <si>
@@ -186,12 +167,6 @@
     <t>Nonsense Mediated Decay (NMD) independent of the Exon Junction Complex (EJC)</t>
   </si>
   <si>
-    <t>R-RNO-72689</t>
-  </si>
-  <si>
-    <t>Formation of a pool of free 40S subunits</t>
-  </si>
-  <si>
     <t>MF</t>
   </si>
   <si>
@@ -262,13 +237,19 @@
   </si>
   <si>
     <t>C &gt; T</t>
+  </si>
+  <si>
+    <t>GO:0005788</t>
+  </si>
+  <si>
+    <t>endoplasmic reticulum lumen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -300,6 +281,18 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF363636"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -321,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -338,6 +331,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,24 +676,24 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -714,7 +710,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -731,24 +727,24 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1080,13 +1076,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -1113,13 +1109,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D3">
         <v>56</v>
@@ -1146,13 +1142,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D4">
         <v>56</v>
@@ -1179,13 +1175,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
         <v>48</v>
-      </c>
-      <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
       </c>
       <c r="D5">
         <v>55</v>
@@ -1212,13 +1208,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D6">
         <v>48</v>
@@ -1286,103 +1282,61 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="8">
+      <c r="B2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="8">
-        <v>35</v>
-      </c>
-      <c r="F2" s="8">
-        <v>0.62168999999999996</v>
-      </c>
-      <c r="G2" s="8">
-        <v>2.0036</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="D2" s="11">
+        <v>23</v>
+      </c>
+      <c r="E2" s="11">
+        <v>9</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-0.69891999999999999</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2.1114000000000002</v>
+      </c>
+      <c r="H2" s="12">
         <v>2.2E-16</v>
       </c>
-      <c r="I2" s="8">
-        <v>4.4352000000000003E-3</v>
-      </c>
-      <c r="J2" s="7">
+      <c r="I2" s="11">
+        <v>8.1668999999999995E-3</v>
+      </c>
+      <c r="J2" s="10">
         <f>-LOG10(I2)</f>
-        <v>2.3530867914043059</v>
+        <v>2.0879427621186211</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="8">
-        <v>18</v>
-      </c>
-      <c r="E3" s="8">
-        <v>8</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0.73248999999999997</v>
-      </c>
-      <c r="G3" s="8">
-        <v>1.88</v>
-      </c>
-      <c r="H3" s="9">
-        <v>2.2E-16</v>
-      </c>
-      <c r="I3" s="8">
-        <v>2.7165999999999999E-2</v>
-      </c>
-      <c r="J3" s="7">
-        <f t="shared" ref="J3:J4" si="0">-LOG10(I3)</f>
-        <v>1.5659743036437535</v>
-      </c>
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="8">
-        <v>12</v>
-      </c>
-      <c r="E4" s="8">
-        <v>2</v>
-      </c>
-      <c r="F4" s="8">
-        <v>0.79200000000000004</v>
-      </c>
-      <c r="G4" s="8">
-        <v>1.8465</v>
-      </c>
-      <c r="H4" s="8">
-        <v>1.4224999999999999E-3</v>
-      </c>
-      <c r="I4" s="8">
-        <v>3.1415999999999999E-2</v>
-      </c>
-      <c r="J4" s="7">
-        <f t="shared" si="0"/>
-        <v>1.5028491117376381</v>
-      </c>
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
@@ -1498,435 +1452,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B682E7-D843-764E-ABF2-E00C52974D71}">
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2">
-        <v>57</v>
-      </c>
-      <c r="D2">
-        <v>31</v>
-      </c>
-      <c r="E2">
-        <v>0.58435999999999999</v>
-      </c>
-      <c r="F2">
-        <v>1.8732</v>
-      </c>
-      <c r="G2" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H2">
-        <v>2.0383999999999999E-2</v>
-      </c>
-      <c r="I2">
-        <f>-LOG10(H2)</f>
-        <v>1.6907105893447436</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3">
-        <v>57</v>
-      </c>
-      <c r="D3">
-        <v>31</v>
-      </c>
-      <c r="E3">
-        <v>0.58435999999999999</v>
-      </c>
-      <c r="F3">
-        <v>1.8732</v>
-      </c>
-      <c r="G3" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H3">
-        <v>2.0383999999999999E-2</v>
-      </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I14" si="0">-LOG10(H3)</f>
-        <v>1.6907105893447436</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>60</v>
-      </c>
-      <c r="D4">
-        <v>30</v>
-      </c>
-      <c r="E4">
-        <v>0.57459000000000005</v>
-      </c>
-      <c r="F4">
-        <v>1.8753</v>
-      </c>
-      <c r="G4" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H4">
-        <v>2.3286999999999999E-2</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="0"/>
-        <v>1.6328864568223629</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <v>60</v>
-      </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
-      <c r="E5">
-        <v>0.57459000000000005</v>
-      </c>
-      <c r="F5">
-        <v>1.8753</v>
-      </c>
-      <c r="G5" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H5">
-        <v>2.3286999999999999E-2</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="0"/>
-        <v>1.6328864568223629</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6">
-        <v>60</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>0.57459000000000005</v>
-      </c>
-      <c r="F6">
-        <v>1.8753</v>
-      </c>
-      <c r="G6" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H6">
-        <v>2.3286999999999999E-2</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="0"/>
-        <v>1.6328864568223629</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>30</v>
-      </c>
-      <c r="E7">
-        <v>0.60006000000000004</v>
-      </c>
-      <c r="F7">
-        <v>1.9127000000000001</v>
-      </c>
-      <c r="G7" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H7">
-        <v>2.5836999999999999E-2</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="0"/>
-        <v>1.587757914790086</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8">
-        <v>53</v>
-      </c>
-      <c r="D8">
-        <v>30</v>
-      </c>
-      <c r="E8">
-        <v>0.60006000000000004</v>
-      </c>
-      <c r="F8">
-        <v>1.9127000000000001</v>
-      </c>
-      <c r="G8" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H8">
-        <v>2.5836999999999999E-2</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="0"/>
-        <v>1.587757914790086</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9">
-        <v>54</v>
-      </c>
-      <c r="D9">
-        <v>30</v>
-      </c>
-      <c r="E9">
-        <v>0.59789999999999999</v>
-      </c>
-      <c r="F9">
-        <v>1.8905000000000001</v>
-      </c>
-      <c r="G9" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H9">
-        <v>2.6499000000000002E-2</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="0"/>
-        <v>1.5767705148434314</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10">
-        <v>46</v>
-      </c>
-      <c r="D10">
-        <v>27</v>
-      </c>
-      <c r="E10">
-        <v>0.61577999999999999</v>
-      </c>
-      <c r="F10">
-        <v>1.8984000000000001</v>
-      </c>
-      <c r="G10" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H10">
-        <v>2.7788E-2</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="0"/>
-        <v>1.5561427097976823</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11">
-        <v>74</v>
-      </c>
-      <c r="D11">
-        <v>36</v>
-      </c>
-      <c r="E11">
-        <v>0.55942000000000003</v>
-      </c>
-      <c r="F11">
-        <v>1.8809</v>
-      </c>
-      <c r="G11" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H11">
-        <v>2.9673999999999999E-2</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="0"/>
-        <v>1.5276239076488416</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12">
-        <v>53</v>
-      </c>
-      <c r="D12">
-        <v>31</v>
-      </c>
-      <c r="E12">
-        <v>0.61173</v>
-      </c>
-      <c r="F12">
-        <v>1.929</v>
-      </c>
-      <c r="G12" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H12">
-        <v>3.202E-2</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="0"/>
-        <v>1.4945786724167192</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13">
-        <v>48</v>
-      </c>
-      <c r="D13">
-        <v>29</v>
-      </c>
-      <c r="E13">
-        <v>0.62592000000000003</v>
-      </c>
-      <c r="F13">
-        <v>1.9501999999999999</v>
-      </c>
-      <c r="G13" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H13">
-        <v>3.4780999999999999E-2</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="0"/>
-        <v>1.4586579356099432</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14">
-        <v>49</v>
-      </c>
-      <c r="D14">
-        <v>30</v>
-      </c>
-      <c r="E14">
-        <v>0.63158999999999998</v>
-      </c>
-      <c r="F14">
-        <v>1.9822</v>
-      </c>
-      <c r="G14" s="6">
-        <v>2.2E-16</v>
-      </c>
-      <c r="H14">
-        <v>4.1958000000000002E-2</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>1.3771852213761171</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D05A1A3-502F-C444-83E7-4353255B1706}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1968,10 +1493,10 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D2">
         <v>65</v>
@@ -2001,10 +1526,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D3">
         <v>18</v>
@@ -2034,10 +1559,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -2067,7 +1592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711BBBD6-DC9C-A14C-B161-7177B699CC47}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2103,10 +1628,10 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C2">
         <v>53</v>
@@ -2253,10 +1778,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <v>48</v>
